--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N64_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N64_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.7077078882591</v>
+        <v>5.152502531842104</v>
       </c>
       <c r="D2" t="n">
-        <v>14.77495795987417</v>
+        <v>2.400930668479553</v>
       </c>
       <c r="E2" t="n">
-        <v>10.43394577403981</v>
+        <v>1.695516188281469</v>
       </c>
       <c r="F2" t="n">
-        <v>6.008594904740525</v>
+        <v>0.9763966720203354</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>21.16188124428795</v>
+        <v>3.438805702196792</v>
       </c>
       <c r="D3" t="n">
-        <v>19.54908831629658</v>
+        <v>3.176726851398194</v>
       </c>
       <c r="E3" t="n">
-        <v>10.43394577403981</v>
+        <v>1.695516188281469</v>
       </c>
       <c r="F3" t="n">
-        <v>6.008594904740525</v>
+        <v>0.9763966720203354</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>45.81709214675934</v>
+        <v>7.445277473848393</v>
       </c>
       <c r="D4" t="n">
-        <v>22.14403346902838</v>
+        <v>3.598405438717112</v>
       </c>
       <c r="E4" t="n">
-        <v>10.43394577403981</v>
+        <v>1.695516188281469</v>
       </c>
       <c r="F4" t="n">
-        <v>6.008594904740525</v>
+        <v>0.9763966720203354</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.93947941194365</v>
+        <v>6.490165404440844</v>
       </c>
       <c r="D5" t="n">
-        <v>16.37706726471075</v>
+        <v>2.661273430515497</v>
       </c>
       <c r="E5" t="n">
-        <v>10.43394577403981</v>
+        <v>1.695516188281469</v>
       </c>
       <c r="F5" t="n">
-        <v>6.008594904740525</v>
+        <v>0.9763966720203354</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>41.54577652325569</v>
+        <v>6.751188685029049</v>
       </c>
       <c r="D6" t="n">
-        <v>23.56707501565242</v>
+        <v>3.829649690043519</v>
       </c>
       <c r="E6" t="n">
-        <v>10.43394577403981</v>
+        <v>1.695516188281469</v>
       </c>
       <c r="F6" t="n">
-        <v>6.008594904740525</v>
+        <v>0.9763966720203354</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>14.8071752283568</v>
+        <v>2.406165974607981</v>
       </c>
       <c r="D7" t="n">
-        <v>32.9546383379628</v>
+        <v>5.355128729918955</v>
       </c>
       <c r="E7" t="n">
-        <v>10.43394577403981</v>
+        <v>1.695516188281469</v>
       </c>
       <c r="F7" t="n">
-        <v>6.008594904740525</v>
+        <v>0.9763966720203354</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>30.00120880369766</v>
+        <v>4.87519643060087</v>
       </c>
       <c r="D8" t="n">
-        <v>28.52537834856891</v>
+        <v>4.635373981642449</v>
       </c>
       <c r="E8" t="n">
-        <v>10.43394577403981</v>
+        <v>1.695516188281469</v>
       </c>
       <c r="F8" t="n">
-        <v>6.008594904740525</v>
+        <v>0.9763966720203354</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
